--- a/Requirement/Enzyme Dept Requirments & Changes reg Node.xlsx
+++ b/Requirement/Enzyme Dept Requirments & Changes reg Node.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D794A3A9-4D2F-3E4E-850F-7022730F47C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="33600" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="126">
   <si>
     <t>Page</t>
   </si>
@@ -379,13 +380,28 @@
   </si>
   <si>
     <t>dekhiye agar apko aaj-kal me time mile to connect karke kuchh solve ho sakta hai to ….after that we wont be able to connect till 6 days..</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>excel- done,</t>
+  </si>
+  <si>
+    <t>ye page us samay changes ho sakta hai bolke tok diya tha na</t>
+  </si>
+  <si>
+    <t>software ke andar reverse order me dikhta hai, latest on top, ise bhi change karna hai?</t>
+  </si>
+  <si>
+    <t>pdf check karke review dijiye fir aage dekhenge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,8 +456,15 @@
       <name val="Andalus"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,6 +497,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -547,17 +575,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -573,10 +600,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -594,6 +618,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -606,11 +633,12 @@
     <xf numFmtId="14" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -638,19 +666,25 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3818659</xdr:colOff>
+      <xdr:colOff>4333089</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>173181</xdr:rowOff>
+      <xdr:rowOff>144405</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>164523</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>3763</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>761999</xdr:rowOff>
+      <xdr:rowOff>555422</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -669,8 +703,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7507432" y="18071522"/>
-          <a:ext cx="5706341" cy="762000"/>
+          <a:off x="8544988" y="12241557"/>
+          <a:ext cx="7012256" cy="579815"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -689,12 +723,18 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>510886</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2885</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -734,11 +774,17 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>259773</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>277090</xdr:rowOff>
+      <xdr:rowOff>188191</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -771,9 +817,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -811,9 +857,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -848,7 +894,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -883,7 +929,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,791 +1102,805 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.5" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:9" ht="32">
+      <c r="A1" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" s="4" customFormat="1" ht="19">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:9" s="10" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" s="8" customFormat="1" ht="120">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" s="10" customFormat="1" ht="126" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="F3" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" s="8" customFormat="1" ht="75">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" s="10" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" s="8" customFormat="1" ht="30">
+      <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" s="10" customFormat="1" ht="189" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="F5" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" s="8" customFormat="1" ht="120">
+      <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" s="10" customFormat="1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" s="8" customFormat="1" ht="45">
+      <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" s="10" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" s="8" customFormat="1">
+      <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" s="10" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" s="8" customFormat="1">
+      <c r="A9" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" s="10" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" s="8" customFormat="1" ht="135">
+      <c r="A10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" s="10" customFormat="1" ht="147" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" s="8" customFormat="1" ht="90">
+      <c r="A11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" s="10" customFormat="1" ht="168" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" s="8" customFormat="1" ht="105">
+      <c r="A12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:9" s="10" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" s="8" customFormat="1" ht="60">
+      <c r="A13" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" s="10" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" s="8" customFormat="1" ht="75">
+      <c r="A14" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="8" t="s">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" ht="60">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="13">
         <v>46138</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="C16" s="12"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+    </row>
+    <row r="17" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A17" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="20"/>
+    </row>
+    <row r="18" spans="1:9" ht="45">
+      <c r="A18" s="13">
         <v>46142</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" ht="30">
+      <c r="A19" s="13">
         <v>46142</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="1:9" ht="60">
+      <c r="A20" s="13">
         <v>46142</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" ht="60">
+      <c r="A21" s="13">
         <v>46142</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="13">
         <v>46142</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-    </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" ht="45">
+      <c r="A23" s="13">
         <v>46142</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="84" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" ht="45">
+      <c r="A24" s="13">
         <v>46148</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-    </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="23" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" ht="30">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-    </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-    </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-    </row>
-    <row r="36" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-    </row>
-    <row r="37" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-    </row>
-    <row r="38" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-    </row>
-    <row r="39" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-    </row>
-    <row r="40" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-    </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-    </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-    </row>
-    <row r="44" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-    </row>
-    <row r="45" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-    </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-    </row>
-    <row r="47" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-    </row>
-    <row r="48" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-    </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-    </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
-    </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-    </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-    </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-    </row>
-    <row r="54" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1851,7 +1911,7 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1862,7 +1922,7 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1873,7 +1933,7 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1884,7 +1944,7 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1895,7 +1955,7 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1906,7 +1966,7 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -1917,7 +1977,7 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1928,7 +1988,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1939,7 +1999,7 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1950,7 +2010,7 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1961,7 +2021,7 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1972,7 +2032,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1983,7 +2043,7 @@
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1994,7 +2054,7 @@
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2005,7 +2065,7 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2016,7 +2076,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2027,7 +2087,7 @@
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2038,7 +2098,7 @@
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2049,7 +2109,7 @@
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2060,7 +2120,7 @@
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2071,7 +2131,7 @@
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2082,7 +2142,7 @@
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2093,7 +2153,7 @@
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2104,7 +2164,7 @@
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2115,7 +2175,7 @@
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2126,7 +2186,7 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2137,7 +2197,7 @@
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2148,7 +2208,7 @@
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2159,7 +2219,7 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2170,7 +2230,7 @@
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2181,7 +2241,7 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2192,7 +2252,7 @@
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2203,7 +2263,7 @@
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2214,7 +2274,7 @@
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2225,7 +2285,7 @@
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2236,7 +2296,7 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2247,7 +2307,7 @@
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2258,7 +2318,7 @@
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2269,7 +2329,7 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2280,7 +2340,7 @@
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -2291,7 +2351,7 @@
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -2302,7 +2362,7 @@
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -2313,7 +2373,7 @@
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
     </row>
-    <row r="97" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -2324,7 +2384,7 @@
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -2335,7 +2395,7 @@
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -2346,7 +2406,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -2357,7 +2417,7 @@
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -2368,7 +2428,7 @@
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -2379,7 +2439,7 @@
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -2390,7 +2450,7 @@
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -2401,7 +2461,7 @@
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -2412,7 +2472,7 @@
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -2423,7 +2483,7 @@
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -2434,7 +2494,7 @@
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -2445,7 +2505,7 @@
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -2456,7 +2516,7 @@
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -2467,7 +2527,7 @@
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -2478,7 +2538,7 @@
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -2489,7 +2549,7 @@
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -2500,7 +2560,7 @@
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
     </row>
-    <row r="114" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -2511,7 +2571,7 @@
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
     </row>
-    <row r="115" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -2522,7 +2582,7 @@
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
     </row>
-    <row r="116" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -2545,19 +2605,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:H21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8">
       <c r="C2" t="s">
         <v>16</v>
       </c>
@@ -2577,11 +2637,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
@@ -2600,11 +2660,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
       <c r="D4" t="s">
@@ -2623,11 +2683,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:8">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
@@ -2646,11 +2706,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:8">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="s">
@@ -2666,11 +2726,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
@@ -2686,11 +2746,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>72</v>
       </c>
       <c r="D8" t="s">
@@ -2706,11 +2766,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:8">
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
@@ -2726,11 +2786,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="2:8">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>33</v>
       </c>
       <c r="D10" t="s">
@@ -2746,11 +2806,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="2:8">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
       <c r="D11" t="s">
@@ -2766,11 +2826,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+    <row r="12" spans="2:8">
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>35</v>
       </c>
       <c r="D12" t="s">
@@ -2786,11 +2846,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+    <row r="13" spans="2:8">
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
@@ -2806,9 +2866,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+    <row r="14" spans="2:8">
       <c r="F14" t="s">
         <v>58</v>
       </c>
@@ -2816,33 +2874,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+    <row r="21" spans="2:3">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2850,17 +2884,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3"/>
       <c r="B2" t="s">
         <v>71</v>
       </c>

--- a/Requirement/Enzyme Dept Requirments & Changes reg Node.xlsx
+++ b/Requirement/Enzyme Dept Requirments & Changes reg Node.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D794A3A9-4D2F-3E4E-850F-7022730F47C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1F2BBD-C47C-E848-AD68-4FEAD9A75CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="33600" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="128">
   <si>
     <t>Page</t>
   </si>
@@ -395,13 +395,19 @@
   </si>
   <si>
     <t>pdf check karke review dijiye fir aage dekhenge</t>
+  </si>
+  <si>
+    <t>ye to connec t karke 1 ityem solve karayi thi, same all 5 karni thi</t>
+  </si>
+  <si>
+    <t>ise connect karke dikhayenge, mere pass jo dummy data hai wo hamesha galat hota hai to muskil hai problem samjhna</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,8 +469,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +515,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,11 +593,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -621,6 +640,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -633,12 +655,16 @@
     <xf numFmtId="14" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -659,161 +685,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>4333089</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>144405</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>3763</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>555422</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8544988" y="12241557"/>
-          <a:ext cx="7012256" cy="579815"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>8660</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>17319</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2885</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7524751" y="18885478"/>
-          <a:ext cx="4878532" cy="493567"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>155864</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>43295</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>259773</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>188191</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7671955" y="19448318"/>
-          <a:ext cx="2606386" cy="1298863"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1117,18 +988,18 @@
     <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:9" ht="41">
+      <c r="A1" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" ht="19">
       <c r="A2" s="5" t="s">
@@ -1151,7 +1022,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="120">
+    <row r="3" spans="1:9" s="8" customFormat="1" ht="105">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -1167,7 +1038,7 @@
       <c r="E3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="17" t="s">
         <v>122</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -1190,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="17" t="s">
         <v>121</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -1215,7 +1086,7 @@
       <c r="E5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="17" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
@@ -1257,12 +1128,14 @@
         <v>77</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="F7" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" s="8" customFormat="1">
+    <row r="8" spans="1:9" s="8" customFormat="1" ht="17">
       <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
@@ -1276,14 +1149,14 @@
         <v>14</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="17" t="s">
         <v>121</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" s="8" customFormat="1">
+    <row r="9" spans="1:9" s="8" customFormat="1" ht="17">
       <c r="A9" s="6" t="s">
         <v>78</v>
       </c>
@@ -1297,7 +1170,9 @@
         <v>81</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -1363,7 +1238,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:9" s="8" customFormat="1" ht="60">
+    <row r="13" spans="1:9" s="8" customFormat="1" ht="68">
       <c r="A13" s="9" t="s">
         <v>85</v>
       </c>
@@ -1379,7 +1254,9 @@
       <c r="E13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="F13" s="22" t="s">
+        <v>126</v>
+      </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -1432,17 +1309,17 @@
       <c r="I16" s="12"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9" ht="45">
       <c r="A18" s="13">
@@ -1458,7 +1335,9 @@
         <v>105</v>
       </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="23" t="s">
+        <v>121</v>
+      </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -1477,12 +1356,14 @@
         <v>107</v>
       </c>
       <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="23" t="s">
+        <v>121</v>
+      </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="60">
+    <row r="20" spans="1:9" ht="136">
       <c r="A20" s="13">
         <v>46142</v>
       </c>
@@ -1496,7 +1377,9 @@
         <v>113</v>
       </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
@@ -1515,12 +1398,14 @@
         <v>109</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="23" t="s">
+        <v>121</v>
+      </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" ht="16">
       <c r="A22" s="13">
         <v>46142</v>
       </c>
@@ -1534,7 +1419,9 @@
         <v>111</v>
       </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="23" t="s">
+        <v>121</v>
+      </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
@@ -2600,7 +2487,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
